--- a/task134/golden/care_home_funding_forecast_2027-28.xlsx
+++ b/task134/golden/care_home_funding_forecast_2027-28.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
-  <si>
-    <t>Council-funded care home residents rise to about 790 by 31 March 2028</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+  <si>
+    <t>Council-funded care home residents rise to about 810 by 31 March 2028</t>
   </si>
   <si>
     <t>Strathallan HSCP. Residents in place at the end of each quarter-end day (budget definitions 2.1 to 2.4); records to 31 December 2026.</t>
@@ -43,16 +43,16 @@
     <t>Total, unrounded</t>
   </si>
   <si>
-    <t>On 31 December 2026: 745 council-funded residents; 599 self-funding residents receiving free personal care.</t>
-  </si>
-  <si>
-    <t>Self-funders' moves onto council funding are projected from each resident's months since admission to the home, with deaths and discharges competing; direct admissions at the 2024 to 2026 rate.</t>
-  </si>
-  <si>
-    <t>Council-funded residents in each locality's care homes on 31 December 2026</t>
-  </si>
-  <si>
-    <t>Locality of the home (postcode lookup). Contribution in force on 31 December 2026; contracted weekly fee including supplements. £ a week, per resident.</t>
+    <t>On 31 December 2026: 757 council-funded residents; 581 self-funding residents receiving free personal care.</t>
+  </si>
+  <si>
+    <t>Self-funders' moves onto council funding are projected from each resident's months since admission to the home, with deaths and discharges competing and the capital clocks moved on by the April 2026 and April 2027 rises in the upper capital limit; direct admissions at the 2024 to 2026 rate.</t>
+  </si>
+  <si>
+    <t>A council-funded place costs the partnership £674 to £717 a week residential and £819 to £846 nursing after contributions</t>
+  </si>
+  <si>
+    <t>Locality of the home (postcode lookup). Weekly fee at the 2026-27 contract rate agreed on 6 November 2026, with supplements; contribution in force on 31 December 2026. £ a week, per resident.</t>
   </si>
   <si>
     <t>Locality</t>
@@ -64,10 +64,10 @@
     <t>Residents</t>
   </si>
   <si>
-    <t>Average weekly contribution (£)</t>
-  </si>
-  <si>
-    <t>Average weekly cost to the partnership (£)</t>
+    <t>Average weekly fee (£)</t>
+  </si>
+  <si>
+    <t>Average weekly cost to the partnership after contributions (£)</t>
   </si>
   <si>
     <t>Allanvale</t>
@@ -136,19 +136,25 @@
     <t>Self-funders are the open free personal care awards in the payment lines; months since admission from the admission date on the lines</t>
   </si>
   <si>
+    <t>Capital limits</t>
+  </si>
+  <si>
+    <t>The upper limit rose by £5,000 on 6 April 2026 and rises by £7,000 on 5 April 2027 (charging policy 3.2). 6 April 2026 brought 8 conversions against 1.62 in an ordinary week (the 52 weeks before), 4.81 weeks' worth; 5 April 2027 is taken as 6.73 weeks' worth (7,000 / 5,000 of it): every self-funder's capital reaches the limit that much sooner, those within it converting that day</t>
+  </si>
+  <si>
+    <t>Weekly fee</t>
+  </si>
+  <si>
+    <t>The fee payable under the placement's contract on 31 December 2026 (definitions 3.2): the 2026-27 national rate agreed on 6 November 2026 and backdated to 1 April 2026, plus the resident's supplement; the case system still carries the interim rate on 2026-27 episodes. The 2027-28 draft rates are not agreed and are not used</t>
+  </si>
+  <si>
     <t>Contribution</t>
   </si>
   <si>
     <t>The assessment in force on 31 December 2026 across all of a resident's debtor references (definitions 3.1); reviews completed early but effective in 2027 are not in force</t>
   </si>
   <si>
-    <t>Weekly fee</t>
-  </si>
-  <si>
-    <t>The placement's contracted fee on 31 December 2026 including supplements (definitions 3.2); the 2027-28 draft contract rates are not agreed and are not used</t>
-  </si>
-  <si>
-    <t>The locality of the home, from its postcode in the care home register and the postcode lookup; the locality on the placement is the arranging team's</t>
+    <t>The locality of the home, from its postcode in the care home register and the postcode lookup; the locality on the placement is the team holding the case</t>
   </si>
   <si>
     <t>Rounding</t>
@@ -603,19 +609,19 @@
         <v>46568</v>
       </c>
       <c r="B5" s="5">
-        <v>760</v>
+        <v>790</v>
       </c>
       <c r="C5" s="6">
-        <v>621.1</v>
+        <v>631.6</v>
       </c>
       <c r="D5" s="6">
         <v>84.5</v>
       </c>
       <c r="E5" s="6">
-        <v>53.5</v>
+        <v>75.5</v>
       </c>
       <c r="F5" s="6">
-        <v>759.07</v>
+        <v>791.54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -623,19 +629,19 @@
         <v>46660</v>
       </c>
       <c r="B6" s="5">
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="C6" s="6">
-        <v>567.6</v>
+        <v>577.5</v>
       </c>
       <c r="D6" s="6">
         <v>120.9</v>
       </c>
       <c r="E6" s="6">
-        <v>82</v>
+        <v>102.6</v>
       </c>
       <c r="F6" s="6">
-        <v>770.52</v>
+        <v>801.04</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -643,19 +649,19 @@
         <v>46752</v>
       </c>
       <c r="B7" s="5">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="C7" s="6">
-        <v>518.5</v>
+        <v>527.8</v>
       </c>
       <c r="D7" s="6">
         <v>154.1</v>
       </c>
       <c r="E7" s="6">
-        <v>107.5</v>
+        <v>126.4</v>
       </c>
       <c r="F7" s="6">
-        <v>780.08</v>
+        <v>808.31</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -663,19 +669,19 @@
         <v>46843</v>
       </c>
       <c r="B8" s="5">
-        <v>790</v>
+        <v>810</v>
       </c>
       <c r="C8" s="6">
-        <v>474.2</v>
+        <v>483</v>
       </c>
       <c r="D8" s="6">
         <v>183.9</v>
       </c>
       <c r="E8" s="6">
-        <v>130.8</v>
+        <v>145.4</v>
       </c>
       <c r="F8" s="6">
-        <v>788.96</v>
+        <v>812.3</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -702,8 +708,8 @@
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -716,7 +722,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -741,13 +747,13 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D5" s="8">
-        <v>280</v>
+        <v>954</v>
       </c>
       <c r="E5" s="8">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -758,10 +764,10 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D6" s="8">
-        <v>259</v>
+        <v>1079</v>
       </c>
       <c r="E6" s="8">
         <v>819</v>
@@ -775,13 +781,13 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" s="8">
-        <v>246</v>
+        <v>959</v>
       </c>
       <c r="E7" s="8">
-        <v>709</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -795,7 +801,7 @@
         <v>42</v>
       </c>
       <c r="D8" s="8">
-        <v>259</v>
+        <v>1080</v>
       </c>
       <c r="E8" s="8">
         <v>821</v>
@@ -809,13 +815,13 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9" s="8">
-        <v>238</v>
+        <v>951</v>
       </c>
       <c r="E9" s="8">
-        <v>713</v>
+        <v>702</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -829,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="D10" s="8">
-        <v>251</v>
+        <v>1074</v>
       </c>
       <c r="E10" s="8">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -843,13 +849,13 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" s="8">
-        <v>275</v>
+        <v>954</v>
       </c>
       <c r="E11" s="8">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -863,10 +869,10 @@
         <v>55</v>
       </c>
       <c r="D12" s="8">
-        <v>248</v>
+        <v>1083</v>
       </c>
       <c r="E12" s="8">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -877,13 +883,13 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D13" s="8">
-        <v>252</v>
+        <v>955</v>
       </c>
       <c r="E13" s="8">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -894,13 +900,13 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="8">
-        <v>254</v>
+        <v>1091</v>
       </c>
       <c r="E14" s="8">
-        <v>837</v>
+        <v>846</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -916,7 +922,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A8BCA0-3CC0-4943-852B-D98C2BBD292C}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -997,18 +1003,26 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
